--- a/master/result/92_穿越王朝_凤临天下/92_穿越王朝_凤临天下.xlsx
+++ b/master/result/92_穿越王朝_凤临天下/92_穿越王朝_凤临天下.xlsx
@@ -397,423 +397,535 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:D37"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>memorial</v>
       </c>
       <c r="B2" t="str">
-        <v>memorial</v>
+        <v>/memorial/</v>
       </c>
       <c r="C2" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>纪念碑</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>feudal</v>
       </c>
       <c r="B3" t="str">
-        <v>feudal</v>
+        <v>/feudal/</v>
       </c>
       <c r="C3" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>封建</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>maiden</v>
       </c>
       <c r="B4" t="str">
-        <v>maiden</v>
+        <v>/maiden/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>少女</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>recall</v>
       </c>
       <c r="B5" t="str">
-        <v>recall</v>
+        <v>/rɪˈkɔːl/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>回忆</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>formal</v>
       </c>
       <c r="B6" t="str">
-        <v>formal</v>
+        <v>/formal/</v>
       </c>
       <c r="C6" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>正式</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>article</v>
       </c>
       <c r="B7" t="str">
-        <v>article</v>
+        <v>/ˈɑːtɪkəl/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>物件</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>entrance</v>
       </c>
       <c r="B8" t="str">
-        <v>entrance</v>
+        <v>/entrance/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>入口</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>construction</v>
       </c>
       <c r="B9" t="str">
-        <v>construction</v>
+        <v>/kənˈstrʌkʃn/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>建筑</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>literacy</v>
       </c>
       <c r="B10" t="str">
-        <v>literacy</v>
+        <v>/literacy/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>有文化</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>associate</v>
       </c>
       <c r="B11" t="str">
-        <v>associate</v>
+        <v>/associate/</v>
       </c>
       <c r="C11" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D11" t="str">
         <v>联合</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>esteem</v>
       </c>
       <c r="B12" t="str">
-        <v>esteem</v>
+        <v>/esteem/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>尊敬</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>positive</v>
       </c>
       <c r="B13" t="str">
-        <v>positive</v>
+        <v>/positive/</v>
       </c>
       <c r="C13" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>肯定</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>deliberate</v>
       </c>
       <c r="B14" t="str">
-        <v>deliberate</v>
+        <v>/deliberate/</v>
       </c>
       <c r="C14" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D14" t="str">
         <v>深思熟虑</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>however</v>
       </c>
       <c r="B15" t="str">
-        <v>however</v>
+        <v>/however/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>然而</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>alarm</v>
       </c>
       <c r="B16" t="str">
-        <v>alarm</v>
+        <v>/alarm/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>警报</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>aware</v>
       </c>
       <c r="B17" t="str">
-        <v>aware</v>
+        <v>/aware/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>意识到</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>elevate</v>
       </c>
       <c r="B18" t="str">
-        <v>elevate</v>
+        <v>/elevate/</v>
       </c>
       <c r="C18" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D18" t="str">
         <v>提升</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>coalition</v>
       </c>
       <c r="B19" t="str">
-        <v>coalition</v>
+        <v>/coalition/</v>
       </c>
       <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>联盟</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>full</v>
       </c>
       <c r="B20" t="str">
-        <v>full</v>
+        <v>/full/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>充满</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>though</v>
       </c>
       <c r="B21" t="str">
-        <v>though</v>
+        <v>/though/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>虽然</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>evolve</v>
       </c>
       <c r="B22" t="str">
-        <v>evolve</v>
+        <v>/ɪˈvɒlv/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>发展</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>affirm</v>
       </c>
       <c r="B23" t="str">
-        <v>affirm</v>
+        <v>/affirm/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>确认</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>selfish</v>
       </c>
       <c r="B24" t="str">
-        <v>selfish</v>
+        <v>/selfish/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>自私</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>beam</v>
       </c>
       <c r="B25" t="str">
-        <v>beam</v>
+        <v>/beam/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>梁</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>bearing</v>
       </c>
       <c r="B26" t="str">
-        <v>bearing</v>
+        <v>/bearing/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>举止</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>additional</v>
       </c>
       <c r="B27" t="str">
-        <v>additional</v>
+        <v>/additional/</v>
       </c>
       <c r="C27" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D27" t="str">
         <v>额外的</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>thorn</v>
       </c>
       <c r="B28" t="str">
-        <v>thorn</v>
+        <v>/thorn/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>荆棘</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>supermarket</v>
       </c>
       <c r="B29" t="str">
-        <v>supermarket</v>
+        <v>/supermarket/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>市场</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>kick</v>
       </c>
       <c r="B30" t="str">
-        <v>kick</v>
+        <v>/kɪk/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>踢</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>charge</v>
       </c>
       <c r="B31" t="str">
-        <v>charge</v>
+        <v>/tʃɑːdʒ/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>指控</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>flock</v>
       </c>
       <c r="B32" t="str">
-        <v>flock</v>
+        <v>/flock/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>人群</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>circle</v>
       </c>
       <c r="B33" t="str">
-        <v>circle</v>
+        <v>/ˈsɜːkəl/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>圆周</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>strawberry</v>
       </c>
       <c r="B34" t="str">
-        <v>strawberry</v>
+        <v>/strawberry/</v>
       </c>
       <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>草莓</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>honey</v>
       </c>
       <c r="B35" t="str">
-        <v>honey</v>
+        <v>/honey/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>蜂蜜</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>you</v>
       </c>
       <c r="B36" t="str">
-        <v>you</v>
+        <v>/you/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>你</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>pierce</v>
       </c>
       <c r="B37" t="str">
-        <v>pierce</v>
+        <v>/pierce/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>刺穿</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D37"/>
   </ignoredErrors>
 </worksheet>
 </file>